--- a/Output/data_dictionary_merged_final.xlsx
+++ b/Output/data_dictionary_merged_final.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -719,21 +719,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>age_group_at_death</t>
+          <t>va_done</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Age group at Death (Years)</t>
+          <t>Verbal Autopsy Done</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>fct</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E16">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -742,21 +742,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cause_of_death_new</t>
+          <t>time_to_va</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cause of death</t>
+          <t>Number of Days from Death date taken to do Verbal Autopsy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="18">
@@ -765,20 +765,66 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>age_group_at_death</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Age group at Death (Years)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>cause_of_death_new</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cause of death</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>chr</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>general_cause_of_death</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>General Cause of death</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>chr</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E20">
         <v>0</v>
       </c>
     </row>
